--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DDV_HRM-2031-0200/Panel-28/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DDV_HRM-2031-0200/Panel-28/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,17 +434,17 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -456,26 +456,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.32768</v>
+        <v>17.14138</v>
       </c>
       <c r="D2" t="n">
-        <v>16.18474</v>
+        <v>16.62492</v>
       </c>
       <c r="E2" t="n">
-        <v>17.17235</v>
+        <v>16.75453</v>
       </c>
       <c r="F2" t="n">
-        <v>22.54329</v>
+        <v>42.95834</v>
       </c>
       <c r="G2" t="n">
-        <v>22.66875</v>
+        <v>0.05153</v>
       </c>
       <c r="H2" t="n">
-        <v>34.34675</v>
+        <v>1.8423</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.10754</v>
+        <v>17.12617</v>
       </c>
       <c r="D3" t="n">
-        <v>16.34988</v>
+        <v>17.01063</v>
       </c>
       <c r="E3" t="n">
-        <v>16.47052</v>
+        <v>17.01333</v>
       </c>
       <c r="F3" t="n">
-        <v>22.03024</v>
+        <v>43.42056</v>
       </c>
       <c r="G3" t="n">
-        <v>21.74632</v>
+        <v>0.05168</v>
       </c>
       <c r="H3" t="n">
-        <v>34.4368</v>
+        <v>1.85276</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.07452</v>
+        <v>17.14024</v>
       </c>
       <c r="D4" t="n">
-        <v>16.41318</v>
+        <v>17.02706</v>
       </c>
       <c r="E4" t="n">
-        <v>16.73063</v>
+        <v>17.0308</v>
       </c>
       <c r="F4" t="n">
-        <v>21.88825</v>
+        <v>42.53728</v>
       </c>
       <c r="G4" t="n">
-        <v>21.99855</v>
+        <v>0.05147</v>
       </c>
       <c r="H4" t="n">
-        <v>34.58007</v>
+        <v>1.86824</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.09557</v>
+        <v>17.30276</v>
       </c>
       <c r="D5" t="n">
-        <v>16.46126</v>
+        <v>17.06317</v>
       </c>
       <c r="E5" t="n">
-        <v>17.05312</v>
+        <v>17.28837</v>
       </c>
       <c r="F5" t="n">
-        <v>22.26363</v>
+        <v>44.04279</v>
       </c>
       <c r="G5" t="n">
-        <v>22.06053</v>
+        <v>0.05227</v>
       </c>
       <c r="H5" t="n">
-        <v>34.88697</v>
+        <v>1.85265</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.0191</v>
+        <v>17.03427</v>
       </c>
       <c r="D6" t="n">
-        <v>15.91354</v>
+        <v>16.67054</v>
       </c>
       <c r="E6" t="n">
-        <v>16.45829</v>
+        <v>16.85015</v>
       </c>
       <c r="F6" t="n">
-        <v>21.92036</v>
+        <v>42.63688</v>
       </c>
       <c r="G6" t="n">
-        <v>22.20594</v>
+        <v>0.05066</v>
       </c>
       <c r="H6" t="n">
-        <v>34.96342</v>
+        <v>1.79733</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.83784</v>
+        <v>17.22981</v>
       </c>
       <c r="D7" t="n">
-        <v>15.99924</v>
+        <v>16.69246</v>
       </c>
       <c r="E7" t="n">
-        <v>16.69851</v>
+        <v>16.91633</v>
       </c>
       <c r="F7" t="n">
-        <v>21.76328</v>
+        <v>43.93795</v>
       </c>
       <c r="G7" t="n">
-        <v>22.24251</v>
+        <v>0.05204</v>
       </c>
       <c r="H7" t="n">
-        <v>35.18103</v>
+        <v>1.87616</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.24293</v>
+        <v>17.32808</v>
       </c>
       <c r="D8" t="n">
-        <v>16.11312</v>
+        <v>16.84148</v>
       </c>
       <c r="E8" t="n">
-        <v>16.3754</v>
+        <v>17.0771</v>
       </c>
       <c r="F8" t="n">
-        <v>22.03532</v>
+        <v>43.60162</v>
       </c>
       <c r="G8" t="n">
-        <v>22.29178</v>
+        <v>0.0507</v>
       </c>
       <c r="H8" t="n">
-        <v>35.08759</v>
+        <v>1.85318</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.18218</v>
+        <v>17.01626</v>
       </c>
       <c r="D9" t="n">
-        <v>16.18899</v>
+        <v>16.68754</v>
       </c>
       <c r="E9" t="n">
-        <v>16.67513</v>
+        <v>16.8436</v>
       </c>
       <c r="F9" t="n">
-        <v>22.04828</v>
+        <v>43.80386</v>
       </c>
       <c r="G9" t="n">
-        <v>22.33362</v>
+        <v>0.05142</v>
       </c>
       <c r="H9" t="n">
-        <v>34.89538</v>
+        <v>1.83387</v>
       </c>
     </row>
     <row r="10">
@@ -660,63 +660,53 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.53039</v>
+        <v>17.21047</v>
       </c>
       <c r="D10" t="n">
-        <v>16.4271</v>
+        <v>16.61717</v>
       </c>
       <c r="E10" t="n">
-        <v>16.84656</v>
+        <v>16.94514</v>
       </c>
       <c r="F10" t="n">
-        <v>22.32462</v>
+        <v>43.18809</v>
       </c>
       <c r="G10" t="n">
-        <v>21.81796</v>
+        <v>0.05139</v>
       </c>
       <c r="H10" t="n">
-        <v>34.94881</v>
+        <v>1.85696</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Rz mean</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rz min</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ra mean</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Ra max</t>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -728,32 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>roughness</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.77978</v>
+        <v>17.35339</v>
       </c>
       <c r="D12" t="n">
-        <v>0.08169</v>
+        <v>16.86979</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6141</v>
+        <v>16.93186</v>
       </c>
       <c r="F12" t="n">
-        <v>0.97877</v>
+        <v>43.74206</v>
       </c>
       <c r="G12" t="n">
-        <v>0.11004</v>
+        <v>0.05176</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00776</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.09286</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.12851</v>
+        <v>1.83201</v>
       </c>
     </row>
     <row r="13">
@@ -763,28 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.75942</v>
+        <v>17.06317</v>
       </c>
       <c r="D13" t="n">
-        <v>0.08303000000000001</v>
+        <v>16.95604</v>
       </c>
       <c r="E13" t="n">
-        <v>0.62265</v>
+        <v>17.00246</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9739</v>
+        <v>42.94014</v>
       </c>
       <c r="G13" t="n">
-        <v>0.10949</v>
+        <v>0.05136</v>
       </c>
       <c r="H13" t="n">
-        <v>0.00757</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.09520000000000001</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.12809</v>
+        <v>1.85474</v>
       </c>
     </row>
     <row r="14">
@@ -794,28 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.76107</v>
+        <v>17.18926</v>
       </c>
       <c r="D14" t="n">
-        <v>0.08341999999999999</v>
+        <v>16.83611</v>
       </c>
       <c r="E14" t="n">
-        <v>0.62043</v>
+        <v>17.07982</v>
       </c>
       <c r="F14" t="n">
-        <v>0.99948</v>
+        <v>43.89124</v>
       </c>
       <c r="G14" t="n">
-        <v>0.10878</v>
+        <v>0.05043</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00763</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.09408</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.12876</v>
+        <v>1.88203</v>
       </c>
     </row>
     <row r="15">
@@ -825,28 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.75691</v>
+        <v>16.99007</v>
       </c>
       <c r="D15" t="n">
-        <v>0.08123</v>
+        <v>16.83708</v>
       </c>
       <c r="E15" t="n">
-        <v>0.60427</v>
+        <v>16.97275</v>
       </c>
       <c r="F15" t="n">
-        <v>0.99453</v>
+        <v>42.42705</v>
       </c>
       <c r="G15" t="n">
-        <v>0.10939</v>
+        <v>0.05164</v>
       </c>
       <c r="H15" t="n">
-        <v>0.007820000000000001</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.09371</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.13122</v>
+        <v>1.87564</v>
       </c>
     </row>
     <row r="16">
@@ -856,28 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.7613799999999999</v>
+        <v>17.16914</v>
       </c>
       <c r="D16" t="n">
-        <v>0.08278000000000001</v>
+        <v>16.71807</v>
       </c>
       <c r="E16" t="n">
-        <v>0.60381</v>
+        <v>16.81676</v>
       </c>
       <c r="F16" t="n">
-        <v>0.99687</v>
+        <v>42.44932</v>
       </c>
       <c r="G16" t="n">
-        <v>0.11285</v>
+        <v>0.05156</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00775</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.0988</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.12946</v>
+        <v>1.89948</v>
       </c>
     </row>
     <row r="17">
@@ -887,28 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.76236</v>
+        <v>17.18261</v>
       </c>
       <c r="D17" t="n">
-        <v>0.08289000000000001</v>
+        <v>16.63567</v>
       </c>
       <c r="E17" t="n">
-        <v>0.61648</v>
+        <v>17.04647</v>
       </c>
       <c r="F17" t="n">
-        <v>0.97026</v>
+        <v>43.27304</v>
       </c>
       <c r="G17" t="n">
-        <v>0.10913</v>
+        <v>0.05091</v>
       </c>
       <c r="H17" t="n">
-        <v>0.00781</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.09743</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.12957</v>
+        <v>1.85275</v>
       </c>
     </row>
     <row r="18">
@@ -918,28 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.75003</v>
+        <v>17.23605</v>
       </c>
       <c r="D18" t="n">
-        <v>0.08395</v>
+        <v>16.94779</v>
       </c>
       <c r="E18" t="n">
-        <v>0.61529</v>
+        <v>17.05804</v>
       </c>
       <c r="F18" t="n">
-        <v>0.99318</v>
+        <v>43.37692</v>
       </c>
       <c r="G18" t="n">
-        <v>0.11002</v>
+        <v>0.05039</v>
       </c>
       <c r="H18" t="n">
-        <v>0.00774</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.09361</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.12914</v>
+        <v>1.89126</v>
       </c>
     </row>
     <row r="19">
@@ -949,28 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.76802</v>
+        <v>17.21889</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0829</v>
+        <v>16.95837</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6212299999999999</v>
+        <v>17.13095</v>
       </c>
       <c r="F19" t="n">
-        <v>0.96702</v>
+        <v>43.23995</v>
       </c>
       <c r="G19" t="n">
-        <v>0.11012</v>
+        <v>0.05045</v>
       </c>
       <c r="H19" t="n">
-        <v>0.00784</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.09533</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.13015</v>
+        <v>1.87164</v>
       </c>
     </row>
     <row r="20">
@@ -980,28 +922,482 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.75224</v>
+        <v>17.3596</v>
       </c>
       <c r="D20" t="n">
-        <v>0.08079</v>
+        <v>16.98058</v>
       </c>
       <c r="E20" t="n">
-        <v>0.62469</v>
+        <v>17.32942</v>
       </c>
       <c r="F20" t="n">
-        <v>0.99061</v>
+        <v>43.39545</v>
       </c>
       <c r="G20" t="n">
-        <v>0.11193</v>
+        <v>0.05157</v>
       </c>
       <c r="H20" t="n">
-        <v>0.00772</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.09408999999999999</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.12989</v>
+        <v>1.86742</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.62072</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.13134</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.61761</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.11918</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.60931</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.14294</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.62669</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.13532</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.61959</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.14002</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.6152</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.12921</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.60931</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.15052</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.61592</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.13475</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.6178399999999999</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.15098</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.76933</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.08139</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.61208</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.97253</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.11103</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.007820000000000001</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.09481000000000001</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.12968</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.76701</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.08404</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.61273</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.99271</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.11259</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.00771</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.09415</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.1303</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.74762</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.08196000000000001</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.62825</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.97987</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.11297</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.0078</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.09625</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.12789</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7680399999999999</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.08345</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.6147899999999999</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.99432</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.11051</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.00747</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.09538000000000001</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.12976</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.76013</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.0834</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.6289400000000001</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.99105</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.11236</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.00775</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.09384000000000001</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.12793</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.77527</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.08411</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.6211100000000001</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.97448</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.10988</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.00784</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.09464</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.12657</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7631</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.08251</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.6208900000000001</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.96187</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.11271</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.00765</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.09417</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.12817</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.75552</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.08411</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.61575</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.9746899999999999</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.11182</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.00781</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.09263</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.12821</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.08237</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.62083</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.96832</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.10861</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.00774</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.09307</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.12995</v>
       </c>
     </row>
   </sheetData>
